--- a/business_forms/036_new_location_form--business_forms.xlsx
+++ b/business_forms/036_new_location_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,8 +596,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,12 +625,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'first_name',_'label':_'first_name',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'first_name', 'label': 'first_name', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>first name</t>
         </is>
       </c>
     </row>
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'last_name',_'label':_'last_name',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'last_name', 'label': 'last_name', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>last name</t>
         </is>
       </c>
     </row>
@@ -659,12 +659,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'email',_'label':_'email',_'hint':_none,_'type':_'email',_'options':_[]}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'email', 'label': 'email', 'hint': None, 'type': 'email', 'options': []}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -676,12 +676,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'phone',_'label':_'phone',_'hint':_none,_'type':_'phone',_'options':_[]}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'phone', 'label': 'phone', 'hint': None, 'type': 'phone', 'options': []}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'address',_'label':_'address',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'address', 'label': 'address', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>address</t>
         </is>
       </c>
     </row>
@@ -710,12 +710,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'website',_'label':_'website',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>website</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'website', 'label': 'website', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>website</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'location',_'label':_'location',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'location', 'label': 'location', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>location</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'street',_'label':_'street',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>street</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'street', 'label': 'street', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>street</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'city',_'label':_'city',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'city', 'label': 'city', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>city</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'state',_'label':_'state',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'state', 'label': 'state', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>state</t>
         </is>
       </c>
     </row>
@@ -795,12 +795,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'country',_'label':_'country',_'hint':_none,_'type':_'text',_'options':_[]}</t>
+          <t>country</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'country', 'label': 'country', 'hint': None, 'type': 'text', 'options': []}</t>
+          <t>country</t>
         </is>
       </c>
     </row>
